--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486856_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486856_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0115</v>
+        <v>5.1901</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6984</v>
+        <v>6.6399</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6869</v>
+        <v>-1.4498</v>
       </c>
       <c r="G2" t="n">
         <v>1.7639</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1713</v>
+        <v>1.0073</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0272</v>
+        <v>0.9142</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.144</v>
+        <v>0.0931</v>
       </c>
       <c r="V2" t="n">
         <v>2.0082</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0788</v>
+        <v>2.2427</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2927</v>
+        <v>2.3973</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2139</v>
+        <v>-0.1546</v>
       </c>
       <c r="G3" t="n">
         <v>3.1823</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2821</v>
+        <v>-0.1182</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3253</v>
+        <v>0.4299</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.5481</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>A. MONTERO ISLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6164</v>
+        <v>2.0334</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9806</v>
+        <v>1.8778</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3642</v>
+        <v>0.1555</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.633</v>
+        <v>1.0454</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5831</v>
+        <v>0.8139</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0499</v>
+        <v>0.2314</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7239</v>
+        <v>2.4862</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0263</v>
+        <v>1.421</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7502</v>
+        <v>1.0652</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9091</v>
+        <v>-1.4408</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6094</v>
+        <v>-0.6071</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2996</v>
+        <v>-0.8338</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2053</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.4107</v>
+        <v>-1.4374</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>3.4547</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6963</v>
+        <v>0.5888</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7584</v>
+        <v>0.3643</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5893</v>
+        <v>0.2402</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4189</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MONTERO ISLA</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0121</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9751</v>
+        <v>2.6913</v>
       </c>
       <c r="F5" t="n">
-        <v>0.037</v>
+        <v>-2.1636</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0454</v>
+        <v>1.798</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8139</v>
+        <v>1.9241</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2314</v>
+        <v>-0.1261</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4862</v>
+        <v>3.9416</v>
       </c>
       <c r="K5" t="n">
-        <v>1.421</v>
+        <v>2.5603</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0652</v>
+        <v>1.3813</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4408</v>
+        <v>-2.1435</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6071</v>
+        <v>-0.6362</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8338</v>
+        <v>-1.5074</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.4374</v>
+        <v>-3.4908</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0682</v>
+        <v>0.6044</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3139</v>
+        <v>0.2324</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2458</v>
+        <v>0.3721</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>2.0082</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.4854</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3648</v>
+        <v>0.1169</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5168</v>
+        <v>0.3686</v>
       </c>
       <c r="G6" t="n">
         <v>0.9540999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7302999999999999</v>
+        <v>0.3341</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7514</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0211</v>
+        <v>-0.1694</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4189</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8555</v>
+        <v>0.2896</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9005</v>
+        <v>2.0391</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0451</v>
+        <v>-1.7495</v>
       </c>
       <c r="G7" t="n">
-        <v>1.798</v>
+        <v>-2.633</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9241</v>
+        <v>-1.5831</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1261</v>
+        <v>-1.0499</v>
       </c>
       <c r="J7" t="n">
-        <v>3.9416</v>
+        <v>-0.7239</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5603</v>
+        <v>0.0263</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3813</v>
+        <v>-0.7502</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1435</v>
+        <v>-1.9091</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6362</v>
+        <v>-1.6094</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5074</v>
+        <v>-0.2996</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.4641</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4908</v>
+        <v>-0.4107</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9322</v>
+        <v>2.1279</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4416</v>
+        <v>1.7549</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4906</v>
+        <v>0.3731</v>
       </c>
       <c r="V7" t="n">
         <v>0.5893</v>
       </c>
       <c r="W7" t="n">
-        <v>2.0082</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4189</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ARRIBAS GOMEZ</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1784</v>
+        <v>0.2691</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0269</v>
+        <v>0.6278</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2053</v>
+        <v>-0.3588</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4573</v>
+        <v>-0.4661</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0389</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4184</v>
+        <v>-0.3947</v>
       </c>
       <c r="J8" t="n">
         <v>0.0389</v>
@@ -1060,13 +1060,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4184</v>
+        <v>-0.505</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.1104</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4184</v>
+        <v>-0.3947</v>
       </c>
       <c r="P8" t="n">
         <v>0.2053</v>
@@ -1078,28 +1078,28 @@
         <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4843</v>
+        <v>0.5298</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0659</v>
+        <v>0.3487</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4184</v>
+        <v>0.1811</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>P. ARRIBAS GOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1488</v>
+        <v>0.1784</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4186</v>
+        <v>-0.0269</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2698</v>
+        <v>0.2053</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4661</v>
+        <v>0.4573</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.0389</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3947</v>
+        <v>0.4184</v>
       </c>
       <c r="J9" t="n">
         <v>0.0389</v>
@@ -1138,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.505</v>
+        <v>0.4184</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1104</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3947</v>
+        <v>0.4184</v>
       </c>
       <c r="P9" t="n">
         <v>0.2053</v>
@@ -1156,22 +1156,22 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4095</v>
+        <v>-0.4843</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1395</v>
+        <v>-0.0659</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2701</v>
+        <v>-0.4184</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1042</v>
+        <v>-0.6207</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.615</v>
+        <v>-1.0721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5108</v>
+        <v>0.4515</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9402</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4602</v>
+        <v>-0.0562</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8677</v>
+        <v>0.4106</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4075</v>
+        <v>-0.4668</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0153</v>
+        <v>-1.3974</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6539</v>
+        <v>-3.0065</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6387</v>
+        <v>1.609</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6807</v>
@@ -1312,13 +1312,13 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3245</v>
+        <v>0.9423</v>
       </c>
       <c r="T11" t="n">
-        <v>1.596</v>
+        <v>1.2434</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2715</v>
+        <v>-0.3011</v>
       </c>
       <c r="V11" t="n">
         <v>0.1088</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4431</v>
+        <v>-1.668</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1582</v>
+        <v>-1.472</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2849</v>
+        <v>-0.196</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6965</v>
@@ -1390,13 +1390,13 @@
         <v>0.4107</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8961</v>
+        <v>0.6712</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8368</v>
+        <v>0.523</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0593</v>
+        <v>0.1482</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3317</v>
+        <v>-5.3122</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.8905</v>
+        <v>-4.197</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4413</v>
+        <v>-1.1152</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9954</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9256</v>
+        <v>0.0939</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5851</v>
+        <v>0.1084</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3405</v>
+        <v>-0.0144</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.888800000000002</v>
+        <v>2.218100000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2862</v>
+        <v>6.615599999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.397500000000001</v>
+        <v>-4.397600000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-4.2109</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.935</v>
+        <v>-2.935000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-1.2761</v>
@@ -1546,19 +1546,19 @@
         <v>11.2939</v>
       </c>
       <c r="S14" t="n">
-        <v>6.276</v>
+        <v>6.605300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>6.662500000000001</v>
+        <v>6.991899999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3862000000000002</v>
+        <v>-0.3863</v>
       </c>
       <c r="V14" t="n">
         <v>1.8767</v>
       </c>
       <c r="W14" t="n">
-        <v>5.9157</v>
+        <v>5.915700000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-4.038900000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.4268</v>
+        <v>8.254200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>8.329499999999999</v>
+        <v>7.8065</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0973</v>
+        <v>0.4477</v>
       </c>
       <c r="G15" t="n">
         <v>7.7932</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0361</v>
+        <v>-0.1365</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4802</v>
+        <v>-0.0428</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4441</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.4189</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3377</v>
+        <v>3.3436</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3434</v>
+        <v>0.7618</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9943</v>
+        <v>2.5818</v>
       </c>
       <c r="G16" t="n">
         <v>3.2825</v>
@@ -1702,13 +1702,13 @@
         <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5957</v>
+        <v>-0.5898</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5774</v>
+        <v>-0.159</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0183</v>
+        <v>-0.4308</v>
       </c>
       <c r="V16" t="n">
         <v>0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9606</v>
+        <v>2.2117</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3229</v>
+        <v>0.5321</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6378</v>
+        <v>1.6796</v>
       </c>
       <c r="G17" t="n">
         <v>0.5611</v>
@@ -1780,13 +1780,13 @@
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0994</v>
+        <v>-0.8484</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.651</v>
+        <v>-0.4418</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4484</v>
+        <v>-0.4066</v>
       </c>
       <c r="V17" t="n">
         <v>0.2402</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4724</v>
+        <v>0.6118</v>
       </c>
       <c r="E18" t="n">
         <v>0.5773</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1049</v>
+        <v>0.0346</v>
       </c>
       <c r="G18" t="n">
         <v>0.62</v>
@@ -1858,13 +1858,13 @@
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.616</v>
       </c>
       <c r="T18" t="n">
         <v>-0.124</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6315</v>
+        <v>-0.492</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8295</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5991</v>
+        <v>-0.8589</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6299</v>
+        <v>2.0023</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.229</v>
+        <v>-2.8611</v>
       </c>
       <c r="G19" t="n">
         <v>0.8419</v>
@@ -1936,13 +1936,13 @@
         <v>0.4107</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3537</v>
+        <v>0.0939</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.1742</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4482</v>
+        <v>-0.0803</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7347</v>
+        <v>-1.0025</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4148</v>
+        <v>-1.101</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3199</v>
+        <v>0.0985</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2819</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8368</v>
+        <v>-0.1046</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1899</v>
+        <v>0.1239</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6469</v>
+        <v>-0.2285</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1382</v>
+        <v>-1.2595</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3006</v>
+        <v>-0.196</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8376</v>
+        <v>-1.0634</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6353</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1189</v>
+        <v>-0.2402</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1781</v>
+        <v>0.2827</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.297</v>
+        <v>-0.5229</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4301</v>
+        <v>-1.7746</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5706</v>
+        <v>-2.1522</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1405</v>
+        <v>0.3776</v>
       </c>
       <c r="G22" t="n">
         <v>-0.701</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7291</v>
+        <v>-0.0736</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2558</v>
+        <v>0.1626</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4734</v>
+        <v>-0.2362</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5893</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8102</v>
+        <v>-3.0066</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3492</v>
+        <v>-0.0354</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.461</v>
+        <v>-2.9712</v>
       </c>
       <c r="G23" t="n">
         <v>-3.1443</v>
@@ -2248,13 +2248,13 @@
         <v>1.2321</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7194</v>
+        <v>0.0843</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0541</v>
+        <v>0.3679</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7735</v>
+        <v>-0.2836</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3739</v>
+        <v>-4.9214</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1702</v>
+        <v>-3.7978</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2038</v>
+        <v>-1.1236</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1255</v>
@@ -2326,13 +2326,13 @@
         <v>1.6427</v>
       </c>
       <c r="S24" t="n">
-        <v>0.189</v>
+        <v>-0.3584</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6701</v>
+        <v>0.0425</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4811</v>
+        <v>-0.4009</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8887</v>
+        <v>1.597800000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>4.397600000000001</v>
+        <v>4.397600000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.2863</v>
+        <v>-2.7995</v>
       </c>
       <c r="G25" t="n">
         <v>4.210699999999999</v>
@@ -2404,13 +2404,13 @@
         <v>13.3473</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.276</v>
+        <v>-2.7893</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3862999999999998</v>
+        <v>0.3862</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.6624</v>
+        <v>-3.1755</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8767</v>
